--- a/data/trans_camb/P6905-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 23,89</t>
+          <t>-1,96; 24,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 24,12</t>
+          <t>-4,62; 23,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 17,11</t>
+          <t>-13,06; 16,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 47,04</t>
+          <t>-1,39; 47,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 40,23</t>
+          <t>-6,71; 40,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 20,8</t>
+          <t>-19,52; 19,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 26,86</t>
+          <t>4,72; 27,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 25,51</t>
+          <t>1,08; 26,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 14,34</t>
+          <t>-6,6; 15,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 251,54</t>
+          <t>-11,76; 291,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 252,35</t>
+          <t>-28,58; 262,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,32; 168,83</t>
+          <t>-67,7; 173,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 330,71</t>
+          <t>-6,29; 359,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 267,24</t>
+          <t>-20,7; 269,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 165,2</t>
+          <t>-47,46; 131,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 217,75</t>
+          <t>14,31; 212,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 195,14</t>
+          <t>2,08; 192,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 115,95</t>
+          <t>-29,68; 132,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 6,51</t>
+          <t>-17,73; 6,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 2,98</t>
+          <t>-20,72; 3,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 5,81</t>
+          <t>-18,85; 5,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 27,22</t>
+          <t>-12,16; 25,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 10,23</t>
+          <t>-26,03; 10,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 11,09</t>
+          <t>-21,55; 11,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 11,25</t>
+          <t>-7,92; 12,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 3,92</t>
+          <t>-15,98; 3,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 5,0</t>
+          <t>-12,44; 5,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 26,77</t>
+          <t>-51,94; 28,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 13,5</t>
+          <t>-58,61; 18,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 23,4</t>
+          <t>-54,26; 23,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 97,82</t>
+          <t>-22,13; 89,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 34,59</t>
+          <t>-55,18; 35,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 41,84</t>
+          <t>-42,36; 43,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 38,02</t>
+          <t>-22,01; 45,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 14,05</t>
+          <t>-44,09; 13,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 18,65</t>
+          <t>-33,77; 20,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 14,34</t>
+          <t>-13,35; 14,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 12,82</t>
+          <t>-13,42; 13,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 4,16</t>
+          <t>-25,31; 3,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 5,12</t>
+          <t>-34,45; 4,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 14,9</t>
+          <t>-21,99; 16,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 3,99</t>
+          <t>-44,35; 2,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 8,14</t>
+          <t>-14,91; 8,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 10,71</t>
+          <t>-10,44; 11,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 2,16</t>
+          <t>-26,53; 2,48</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 60,56</t>
+          <t>-37,61; 65,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 55,32</t>
+          <t>-35,13; 59,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,56; 18,53</t>
+          <t>-68,92; 19,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 13,64</t>
+          <t>-60,8; 12,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 42,85</t>
+          <t>-39,28; 45,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 10,34</t>
+          <t>-79,21; 4,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,1; 26,55</t>
+          <t>-38,74; 29,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 36,68</t>
+          <t>-25,32; 38,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 5,82</t>
+          <t>-67,09; 7,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-27,58; -1,79</t>
+          <t>-26,75; -1,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 5,86</t>
+          <t>-20,07; 4,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 4,43</t>
+          <t>-21,64; 4,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 8,83</t>
+          <t>-24,8; 7,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 17,61</t>
+          <t>-15,39; 19,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 5,66</t>
+          <t>-21,56; 9,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,69; -2,65</t>
+          <t>-22,7; -1,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 8,04</t>
+          <t>-12,65; 7,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 2,1</t>
+          <t>-17,38; 1,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,98; -5,06</t>
+          <t>-62,15; -2,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,96; 16,56</t>
+          <t>-46,67; 13,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 12,88</t>
+          <t>-50,43; 14,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 24,5</t>
+          <t>-48,25; 22,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 47,04</t>
+          <t>-29,55; 54,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 15,55</t>
+          <t>-42,57; 24,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,42; -6,63</t>
+          <t>-50,42; -4,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 22,61</t>
+          <t>-28,65; 21,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 6,05</t>
+          <t>-39,09; 4,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 2,25</t>
+          <t>-9,85; 2,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 3,71</t>
+          <t>-9,14; 4,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -0,03</t>
+          <t>-13,78; -0,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 10,02</t>
+          <t>-9,5; 9,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 9,98</t>
+          <t>-9,64; 9,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -0,22</t>
+          <t>-19,53; 0,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 4,73</t>
+          <t>-6,75; 3,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,86</t>
+          <t>-6,1; 4,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,23</t>
+          <t>-11,74; -0,66</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 9,38</t>
+          <t>-30,45; 10,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 13,67</t>
+          <t>-28,7; 15,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 0,23</t>
+          <t>-41,48; -0,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 27,22</t>
+          <t>-21,26; 25,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 27,17</t>
+          <t>-20,72; 26,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -1,26</t>
+          <t>-43,83; 0,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 15,97</t>
+          <t>-18,98; 11,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 12,36</t>
+          <t>-16,91; 15,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,56; -3,69</t>
+          <t>-32,19; -2,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6905-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>4,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 24,02</t>
+          <t>-2,52; 25,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 23,32</t>
+          <t>-6,14; 23,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 16,05</t>
+          <t>-11,52; 17,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 47,48</t>
+          <t>0,46; 46,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 40,28</t>
+          <t>-5,7; 43,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 19,24</t>
+          <t>-16,95; 19,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 27,27</t>
+          <t>3,41; 27,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 26,16</t>
+          <t>-0,03; 26,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 15,7</t>
+          <t>-6,62; 15,86</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 291,68</t>
+          <t>-17,43; 287,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 262,76</t>
+          <t>-34,65; 240,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 173,06</t>
+          <t>-61,36; 183,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 359,02</t>
+          <t>-0,57; 313,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 269,17</t>
+          <t>-17,92; 284,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 131,71</t>
+          <t>-43,77; 138,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 212,67</t>
+          <t>6,62; 214,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 192,25</t>
+          <t>-1,9; 223,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 132,63</t>
+          <t>-32,92; 117,37</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>-1,83</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,92</t>
+          <t>-6,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>-1,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,69</t>
+          <t>-17,97; 5,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 3,73</t>
+          <t>-20,14; 4,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 5,48</t>
+          <t>-13,57; 10,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 25,64</t>
+          <t>-9,18; 27,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 10,4</t>
+          <t>-25,94; 11,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 11,18</t>
+          <t>-21,88; 9,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 12,75</t>
+          <t>-9,61; 12,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 3,67</t>
+          <t>-16,74; 3,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 5,43</t>
+          <t>-10,52; 8,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-23,13%</t>
+          <t>-6,19%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,43%</t>
+          <t>-15,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-12,12%</t>
+          <t>-6,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 28,95</t>
+          <t>-52,27; 22,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,61; 18,7</t>
+          <t>-58,87; 20,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,26; 23,57</t>
+          <t>-42,03; 43,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 89,27</t>
+          <t>-18,29; 98,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 35,16</t>
+          <t>-53,63; 37,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 43,37</t>
+          <t>-43,32; 33,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 45,57</t>
+          <t>-25,84; 45,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 13,3</t>
+          <t>-44,71; 14,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 20,78</t>
+          <t>-29,26; 29,26</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-11,6</t>
+          <t>-8,83</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,97</t>
+          <t>-6,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,27</t>
+          <t>-4,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 14,4</t>
+          <t>-14,33; 15,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 13,37</t>
+          <t>-14,86; 12,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 3,83</t>
+          <t>-23,05; 6,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 4,41</t>
+          <t>-34,2; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 16,64</t>
+          <t>-23,31; 13,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 2,13</t>
+          <t>-25,66; 12,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 8,83</t>
+          <t>-15,08; 8,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 11,02</t>
+          <t>-11,73; 10,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 2,48</t>
+          <t>-16,41; 6,5</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-38,06%</t>
+          <t>-28,98%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-38,77%</t>
+          <t>-13,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-29,18%</t>
+          <t>-11,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 65,47</t>
+          <t>-40,7; 64,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 59,62</t>
+          <t>-37,51; 49,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,92; 19,31</t>
+          <t>-64,39; 30,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,8; 12,45</t>
+          <t>-61,09; 10,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 45,81</t>
+          <t>-41,65; 41,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,21; 4,94</t>
+          <t>-43,59; 36,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 29,59</t>
+          <t>-37,99; 27,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 38,25</t>
+          <t>-28,19; 34,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 7,0</t>
+          <t>-38,47; 22,12</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,0</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,67</t>
+          <t>-12,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,24</t>
+          <t>-10,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,75; -1,85</t>
+          <t>-27,51; -2,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 4,24</t>
+          <t>-21,3; 5,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 4,08</t>
+          <t>-21,17; 3,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 7,9</t>
+          <t>-25,2; 9,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 19,46</t>
+          <t>-14,15; 19,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 9,22</t>
+          <t>-24,67; 0,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,7; -1,7</t>
+          <t>-21,52; -0,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 7,61</t>
+          <t>-15,03; 7,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 1,39</t>
+          <t>-19,55; -1,69</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-23,02%</t>
+          <t>-22,71%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,59%</t>
+          <t>-28,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,05%</t>
+          <t>-24,57%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,15; -2,42</t>
+          <t>-62,05; -8,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 13,92</t>
+          <t>-49,04; 16,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 14,91</t>
+          <t>-49,02; 10,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 22,24</t>
+          <t>-50,39; 25,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 54,94</t>
+          <t>-27,45; 55,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 24,46</t>
+          <t>-48,02; 3,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,42; -4,5</t>
+          <t>-48,55; -2,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 21,45</t>
+          <t>-32,91; 19,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 4,18</t>
+          <t>-41,77; -4,45</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,2</t>
+          <t>-4,81</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,66</t>
+          <t>-7,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-4,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 2,63</t>
+          <t>-10,93; 2,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,05</t>
+          <t>-9,49; 3,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -0,2</t>
+          <t>-11,83; 2,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 9,37</t>
+          <t>-10,16; 9,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 9,53</t>
+          <t>-7,8; 11,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 0,2</t>
+          <t>-15,28; 1,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,8</t>
+          <t>-7,24; 4,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,9</t>
+          <t>-6,47; 3,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -0,66</t>
+          <t>-8,89; 0,72</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-23,97%</t>
+          <t>-16,02%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-21,15%</t>
+          <t>-18,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>-12,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 10,02</t>
+          <t>-33,63; 8,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 15,23</t>
+          <t>-28,6; 12,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -0,59</t>
+          <t>-35,7; 7,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 25,63</t>
+          <t>-22,32; 26,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 26,01</t>
+          <t>-17,72; 32,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 0,0</t>
+          <t>-33,19; 4,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 11,39</t>
+          <t>-19,6; 14,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 15,67</t>
+          <t>-18,03; 12,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,19; -2,0</t>
+          <t>-24,79; 2,47</t>
         </is>
       </c>
     </row>
